--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/trans.beta.carotene/Resultats_trans.beta.carotene_moy.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/trans.beta.carotene/Resultats_trans.beta.carotene_moy.xlsx
@@ -851,26 +851,15 @@
   <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="102.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="34" width="12" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="12" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="12" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="107.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="48" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" x14ac:dyDescent="0.25">
